--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340016</v>
       </c>
       <c r="B2" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340021</v>
       </c>
       <c r="B3" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128340015</v>
       </c>
       <c r="B4" t="n">
-        <v>98488</v>
+        <v>98502</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340019</v>
       </c>
       <c r="B5" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340018</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128340014</v>
       </c>
       <c r="B7" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340016</v>
       </c>
       <c r="B2" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340021</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128340015</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340019</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340018</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128340014</v>
       </c>
       <c r="B7" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128340015</v>
       </c>
       <c r="B4" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1309,6 +1309,1762 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128791250</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92949</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>769524</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7288514</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128791260</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>769511</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7288583</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128791252</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>769512</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7288612</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128791261</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>769432</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7288424</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128791238</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>769514</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7288604</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128791254</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>769524</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7288630</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128791257</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>769534</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7288588</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128791262</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>769410</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7288409</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128791266</v>
+      </c>
+      <c r="B16" t="n">
+        <v>82948</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>769398</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7288351</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128791236</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>769492</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7288482</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128791245</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>769510</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7288640</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128791243</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>769412</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7288353</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128791263</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>769526</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7288515</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>50cm lång</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128791237</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>769415</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7288418</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128791258</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79168</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>864</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>769406</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7288354</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128791264</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>769507</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7288631</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128791242</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>769513</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7288611</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128791244</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>769510</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7288634</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340016</v>
       </c>
       <c r="B2" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128340015</v>
       </c>
       <c r="B4" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128791250</v>
       </c>
       <c r="B8" t="n">
-        <v>92949</v>
+        <v>92950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1801,32 +1801,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791254</v>
+        <v>128791257</v>
       </c>
       <c r="B13" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>769524</v>
+        <v>769534</v>
       </c>
       <c r="R13" t="n">
-        <v>7288630</v>
+        <v>7288588</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1898,32 +1898,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791257</v>
+        <v>128791254</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>769534</v>
+        <v>769524</v>
       </c>
       <c r="R14" t="n">
-        <v>7288588</v>
+        <v>7288630</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2192,7 +2192,7 @@
         <v>128791236</v>
       </c>
       <c r="B17" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128791237</v>
       </c>
       <c r="B21" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791264</v>
+        <v>128791242</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>80223</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769507</v>
+        <v>769513</v>
       </c>
       <c r="R23" t="n">
-        <v>7288631</v>
+        <v>7288611</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2873,7 +2873,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791242</v>
+        <v>128791244</v>
       </c>
       <c r="B24" t="n">
         <v>80223</v>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769513</v>
+        <v>769510</v>
       </c>
       <c r="R24" t="n">
-        <v>7288611</v>
+        <v>7288634</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791244</v>
+        <v>128791264</v>
       </c>
       <c r="B25" t="n">
-        <v>80223</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769510</v>
+        <v>769507</v>
       </c>
       <c r="R25" t="n">
-        <v>7288634</v>
+        <v>7288631</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>128791250</v>
       </c>
       <c r="B8" t="n">
-        <v>92950</v>
+        <v>92977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128791260</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128791252</v>
       </c>
       <c r="B10" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128791261</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128791238</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,32 +1801,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791257</v>
+        <v>128791254</v>
       </c>
       <c r="B13" t="n">
-        <v>98592</v>
+        <v>80221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>769534</v>
+        <v>769524</v>
       </c>
       <c r="R13" t="n">
-        <v>7288588</v>
+        <v>7288630</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1898,32 +1898,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791254</v>
+        <v>128791257</v>
       </c>
       <c r="B14" t="n">
-        <v>80194</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>769524</v>
+        <v>769534</v>
       </c>
       <c r="R14" t="n">
-        <v>7288630</v>
+        <v>7288588</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1998,7 +1998,7 @@
         <v>128791262</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128791266</v>
       </c>
       <c r="B16" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128791236</v>
       </c>
       <c r="B17" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>128791245</v>
       </c>
       <c r="B18" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128791243</v>
+        <v>128791237</v>
       </c>
       <c r="B19" t="n">
-        <v>80223</v>
+        <v>91494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769412</v>
+        <v>769415</v>
       </c>
       <c r="R19" t="n">
-        <v>7288353</v>
+        <v>7288418</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2480,32 +2480,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128791263</v>
+        <v>128791243</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>80250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769526</v>
+        <v>769412</v>
       </c>
       <c r="R20" t="n">
-        <v>7288515</v>
+        <v>7288353</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2551,11 +2551,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2582,10 +2577,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128791237</v>
+        <v>128791263</v>
       </c>
       <c r="B21" t="n">
-        <v>91467</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,21 +2588,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769415</v>
+        <v>769526</v>
       </c>
       <c r="R21" t="n">
-        <v>7288418</v>
+        <v>7288515</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2653,6 +2648,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2682,7 +2682,7 @@
         <v>128791258</v>
       </c>
       <c r="B22" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791242</v>
+        <v>128791264</v>
       </c>
       <c r="B23" t="n">
-        <v>80223</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769513</v>
+        <v>769507</v>
       </c>
       <c r="R23" t="n">
-        <v>7288611</v>
+        <v>7288631</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2876,7 +2876,7 @@
         <v>128791244</v>
       </c>
       <c r="B24" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791264</v>
+        <v>128791242</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>80250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769507</v>
+        <v>769513</v>
       </c>
       <c r="R25" t="n">
-        <v>7288631</v>
+        <v>7288611</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340016</v>
       </c>
       <c r="B2" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340021</v>
       </c>
       <c r="B3" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128340015</v>
       </c>
       <c r="B4" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340019</v>
       </c>
       <c r="B5" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340018</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128340014</v>
       </c>
       <c r="B7" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791264</v>
+        <v>128791242</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>80250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769507</v>
+        <v>769513</v>
       </c>
       <c r="R23" t="n">
-        <v>7288631</v>
+        <v>7288611</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2873,32 +2873,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791244</v>
+        <v>128791264</v>
       </c>
       <c r="B24" t="n">
-        <v>80250</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769510</v>
+        <v>769507</v>
       </c>
       <c r="R24" t="n">
-        <v>7288634</v>
+        <v>7288631</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791242</v>
+        <v>128791244</v>
       </c>
       <c r="B25" t="n">
         <v>80250</v>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769513</v>
+        <v>769510</v>
       </c>
       <c r="R25" t="n">
-        <v>7288611</v>
+        <v>7288634</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>128791250</v>
       </c>
       <c r="B8" t="n">
-        <v>92977</v>
+        <v>92982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791260</v>
+        <v>128791252</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>80225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769511</v>
+        <v>769512</v>
       </c>
       <c r="R9" t="n">
-        <v>7288583</v>
+        <v>7288612</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791252</v>
+        <v>128791260</v>
       </c>
       <c r="B10" t="n">
-        <v>80221</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769512</v>
+        <v>769511</v>
       </c>
       <c r="R10" t="n">
-        <v>7288612</v>
+        <v>7288583</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1605,7 +1605,7 @@
         <v>128791261</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,32 +1801,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791254</v>
+        <v>128791257</v>
       </c>
       <c r="B13" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>769524</v>
+        <v>769534</v>
       </c>
       <c r="R13" t="n">
-        <v>7288630</v>
+        <v>7288588</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1898,32 +1898,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791257</v>
+        <v>128791254</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>769534</v>
+        <v>769524</v>
       </c>
       <c r="R14" t="n">
-        <v>7288588</v>
+        <v>7288630</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1998,7 +1998,7 @@
         <v>128791262</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128791266</v>
       </c>
       <c r="B16" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128791236</v>
       </c>
       <c r="B17" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>128791245</v>
       </c>
       <c r="B18" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128791237</v>
+        <v>128791243</v>
       </c>
       <c r="B19" t="n">
-        <v>91494</v>
+        <v>80254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769415</v>
+        <v>769412</v>
       </c>
       <c r="R19" t="n">
-        <v>7288418</v>
+        <v>7288353</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2480,32 +2480,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128791243</v>
+        <v>128791263</v>
       </c>
       <c r="B20" t="n">
-        <v>80250</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769412</v>
+        <v>769526</v>
       </c>
       <c r="R20" t="n">
-        <v>7288353</v>
+        <v>7288515</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2551,6 +2551,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2577,10 +2582,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128791263</v>
+        <v>128791237</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>91499</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2588,21 +2593,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769526</v>
+        <v>769415</v>
       </c>
       <c r="R21" t="n">
-        <v>7288515</v>
+        <v>7288418</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2648,11 +2653,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2682,7 +2682,7 @@
         <v>128791258</v>
       </c>
       <c r="B22" t="n">
-        <v>79195</v>
+        <v>79199</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791242</v>
+        <v>128791264</v>
       </c>
       <c r="B23" t="n">
-        <v>80250</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769513</v>
+        <v>769507</v>
       </c>
       <c r="R23" t="n">
-        <v>7288611</v>
+        <v>7288631</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2873,32 +2873,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791264</v>
+        <v>128791242</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>80254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769507</v>
+        <v>769513</v>
       </c>
       <c r="R24" t="n">
-        <v>7288631</v>
+        <v>7288611</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2973,7 +2973,7 @@
         <v>128791244</v>
       </c>
       <c r="B25" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340016</v>
       </c>
       <c r="B2" t="n">
-        <v>91514</v>
+        <v>91524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340021</v>
       </c>
       <c r="B3" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128340015</v>
       </c>
       <c r="B4" t="n">
-        <v>98536</v>
+        <v>98549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340019</v>
       </c>
       <c r="B5" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340018</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128340014</v>
       </c>
       <c r="B7" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128791250</v>
       </c>
       <c r="B8" t="n">
-        <v>92982</v>
+        <v>92989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791252</v>
+        <v>128791260</v>
       </c>
       <c r="B9" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769512</v>
+        <v>769511</v>
       </c>
       <c r="R9" t="n">
-        <v>7288612</v>
+        <v>7288583</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791260</v>
+        <v>128791252</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769511</v>
+        <v>769512</v>
       </c>
       <c r="R10" t="n">
-        <v>7288583</v>
+        <v>7288612</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1804,7 +1804,7 @@
         <v>128791257</v>
       </c>
       <c r="B13" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128791236</v>
       </c>
       <c r="B17" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128791243</v>
+        <v>128791237</v>
       </c>
       <c r="B19" t="n">
-        <v>80254</v>
+        <v>91504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769412</v>
+        <v>769415</v>
       </c>
       <c r="R19" t="n">
-        <v>7288353</v>
+        <v>7288418</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2582,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128791237</v>
+        <v>128791243</v>
       </c>
       <c r="B21" t="n">
-        <v>91499</v>
+        <v>80254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769415</v>
+        <v>769412</v>
       </c>
       <c r="R21" t="n">
-        <v>7288418</v>
+        <v>7288353</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791260</v>
+        <v>128791252</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769511</v>
+        <v>769512</v>
       </c>
       <c r="R9" t="n">
-        <v>7288583</v>
+        <v>7288612</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791252</v>
+        <v>128791260</v>
       </c>
       <c r="B10" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769512</v>
+        <v>769511</v>
       </c>
       <c r="R10" t="n">
-        <v>7288612</v>
+        <v>7288583</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1801,32 +1801,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791257</v>
+        <v>128791254</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>769534</v>
+        <v>769524</v>
       </c>
       <c r="R13" t="n">
-        <v>7288588</v>
+        <v>7288630</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1898,32 +1898,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791254</v>
+        <v>128791257</v>
       </c>
       <c r="B14" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>769524</v>
+        <v>769534</v>
       </c>
       <c r="R14" t="n">
-        <v>7288630</v>
+        <v>7288588</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128791237</v>
+        <v>128791243</v>
       </c>
       <c r="B19" t="n">
-        <v>91504</v>
+        <v>80254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769415</v>
+        <v>769412</v>
       </c>
       <c r="R19" t="n">
-        <v>7288418</v>
+        <v>7288353</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2582,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128791243</v>
+        <v>128791237</v>
       </c>
       <c r="B21" t="n">
-        <v>80254</v>
+        <v>91504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769412</v>
+        <v>769415</v>
       </c>
       <c r="R21" t="n">
-        <v>7288353</v>
+        <v>7288418</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -2480,10 +2480,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128791263</v>
+        <v>128791237</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2491,21 +2491,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769526</v>
+        <v>769415</v>
       </c>
       <c r="R20" t="n">
-        <v>7288515</v>
+        <v>7288418</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2551,11 +2551,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2582,10 +2577,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128791237</v>
+        <v>128791263</v>
       </c>
       <c r="B21" t="n">
-        <v>91504</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,21 +2588,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769415</v>
+        <v>769526</v>
       </c>
       <c r="R21" t="n">
-        <v>7288418</v>
+        <v>7288515</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2653,6 +2648,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>128791250</v>
       </c>
       <c r="B8" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791252</v>
+        <v>128791260</v>
       </c>
       <c r="B9" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769512</v>
+        <v>769511</v>
       </c>
       <c r="R9" t="n">
-        <v>7288612</v>
+        <v>7288583</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791260</v>
+        <v>128791252</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>80229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769511</v>
+        <v>769512</v>
       </c>
       <c r="R10" t="n">
-        <v>7288583</v>
+        <v>7288612</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1605,7 +1605,7 @@
         <v>128791261</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128791238</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>128791254</v>
       </c>
       <c r="B13" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>128791257</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>128791262</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128791266</v>
       </c>
       <c r="B16" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128791236</v>
       </c>
       <c r="B17" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>128791245</v>
       </c>
       <c r="B18" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128791243</v>
+        <v>128791237</v>
       </c>
       <c r="B19" t="n">
-        <v>80254</v>
+        <v>91508</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769412</v>
+        <v>769415</v>
       </c>
       <c r="R19" t="n">
-        <v>7288353</v>
+        <v>7288418</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2480,32 +2480,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128791237</v>
+        <v>128791243</v>
       </c>
       <c r="B20" t="n">
-        <v>91504</v>
+        <v>80258</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769415</v>
+        <v>769412</v>
       </c>
       <c r="R20" t="n">
-        <v>7288418</v>
+        <v>7288353</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2580,7 +2580,7 @@
         <v>128791263</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>128791258</v>
       </c>
       <c r="B22" t="n">
-        <v>79199</v>
+        <v>79203</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791264</v>
+        <v>128791242</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>80258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769507</v>
+        <v>769513</v>
       </c>
       <c r="R23" t="n">
-        <v>7288631</v>
+        <v>7288611</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791242</v>
+        <v>128791244</v>
       </c>
       <c r="B24" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769513</v>
+        <v>769510</v>
       </c>
       <c r="R24" t="n">
-        <v>7288611</v>
+        <v>7288634</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791244</v>
+        <v>128791264</v>
       </c>
       <c r="B25" t="n">
-        <v>80254</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769510</v>
+        <v>769507</v>
       </c>
       <c r="R25" t="n">
-        <v>7288634</v>
+        <v>7288631</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340016</v>
       </c>
       <c r="B2" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340021</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128340015</v>
       </c>
       <c r="B4" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128340019</v>
       </c>
       <c r="B5" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128340018</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128340014</v>
       </c>
       <c r="B7" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791260</v>
+        <v>128791252</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769511</v>
+        <v>769512</v>
       </c>
       <c r="R9" t="n">
-        <v>7288583</v>
+        <v>7288612</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791252</v>
+        <v>128791260</v>
       </c>
       <c r="B10" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769512</v>
+        <v>769511</v>
       </c>
       <c r="R10" t="n">
-        <v>7288612</v>
+        <v>7288583</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791252</v>
+        <v>128791260</v>
       </c>
       <c r="B9" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769512</v>
+        <v>769511</v>
       </c>
       <c r="R9" t="n">
-        <v>7288612</v>
+        <v>7288583</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791260</v>
+        <v>128791252</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769511</v>
+        <v>769512</v>
       </c>
       <c r="R10" t="n">
-        <v>7288583</v>
+        <v>7288612</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -2873,32 +2873,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791244</v>
+        <v>128791264</v>
       </c>
       <c r="B24" t="n">
-        <v>80258</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769510</v>
+        <v>769507</v>
       </c>
       <c r="R24" t="n">
-        <v>7288634</v>
+        <v>7288631</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791264</v>
+        <v>128791244</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>80258</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769507</v>
+        <v>769510</v>
       </c>
       <c r="R25" t="n">
-        <v>7288631</v>
+        <v>7288634</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>128791250</v>
       </c>
       <c r="B8" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791260</v>
+        <v>128791252</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>80134</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769511</v>
+        <v>769512</v>
       </c>
       <c r="R9" t="n">
-        <v>7288583</v>
+        <v>7288612</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791252</v>
+        <v>128791260</v>
       </c>
       <c r="B10" t="n">
-        <v>80229</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769512</v>
+        <v>769511</v>
       </c>
       <c r="R10" t="n">
-        <v>7288612</v>
+        <v>7288583</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1605,7 +1605,7 @@
         <v>128791261</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128791238</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,32 +1801,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791254</v>
+        <v>128791257</v>
       </c>
       <c r="B13" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>769524</v>
+        <v>769534</v>
       </c>
       <c r="R13" t="n">
-        <v>7288630</v>
+        <v>7288588</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1898,32 +1898,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791257</v>
+        <v>128791254</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>769534</v>
+        <v>769524</v>
       </c>
       <c r="R14" t="n">
-        <v>7288588</v>
+        <v>7288630</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1998,7 +1998,7 @@
         <v>128791262</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128791266</v>
       </c>
       <c r="B16" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128791236</v>
       </c>
       <c r="B17" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>128791245</v>
       </c>
       <c r="B18" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128791237</v>
+        <v>128791263</v>
       </c>
       <c r="B19" t="n">
-        <v>91508</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2394,21 +2394,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769415</v>
+        <v>769526</v>
       </c>
       <c r="R19" t="n">
-        <v>7288418</v>
+        <v>7288515</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2454,6 +2454,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2480,32 +2485,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128791243</v>
+        <v>128791237</v>
       </c>
       <c r="B20" t="n">
-        <v>80258</v>
+        <v>91513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769412</v>
+        <v>769415</v>
       </c>
       <c r="R20" t="n">
-        <v>7288353</v>
+        <v>7288418</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2577,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128791263</v>
+        <v>128791243</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>80163</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769526</v>
+        <v>769412</v>
       </c>
       <c r="R21" t="n">
-        <v>7288515</v>
+        <v>7288353</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2648,11 +2653,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2682,7 +2682,7 @@
         <v>128791258</v>
       </c>
       <c r="B22" t="n">
-        <v>79203</v>
+        <v>79108</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791242</v>
+        <v>128791264</v>
       </c>
       <c r="B23" t="n">
-        <v>80258</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769513</v>
+        <v>769507</v>
       </c>
       <c r="R23" t="n">
-        <v>7288611</v>
+        <v>7288631</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2873,32 +2873,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791264</v>
+        <v>128791242</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>80163</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769507</v>
+        <v>769513</v>
       </c>
       <c r="R24" t="n">
-        <v>7288631</v>
+        <v>7288611</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2973,7 +2973,7 @@
         <v>128791244</v>
       </c>
       <c r="B25" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791260</v>
+        <v>128791252</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769511</v>
+        <v>769512</v>
       </c>
       <c r="R9" t="n">
-        <v>7288583</v>
+        <v>7288612</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791252</v>
+        <v>128791260</v>
       </c>
       <c r="B10" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769512</v>
+        <v>769511</v>
       </c>
       <c r="R10" t="n">
-        <v>7288612</v>
+        <v>7288583</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>128791250</v>
       </c>
       <c r="B8" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791252</v>
+        <v>128791260</v>
       </c>
       <c r="B9" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769512</v>
+        <v>769511</v>
       </c>
       <c r="R9" t="n">
-        <v>7288612</v>
+        <v>7288583</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791260</v>
+        <v>128791252</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769511</v>
+        <v>769512</v>
       </c>
       <c r="R10" t="n">
-        <v>7288583</v>
+        <v>7288612</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1901,7 +1901,7 @@
         <v>128791257</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128791236</v>
       </c>
       <c r="B17" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128791237</v>
+        <v>128791263</v>
       </c>
       <c r="B19" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2394,21 +2394,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769415</v>
+        <v>769526</v>
       </c>
       <c r="R19" t="n">
-        <v>7288418</v>
+        <v>7288515</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2454,6 +2454,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2480,32 +2485,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128791243</v>
+        <v>128791237</v>
       </c>
       <c r="B20" t="n">
-        <v>80168</v>
+        <v>91523</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769412</v>
+        <v>769415</v>
       </c>
       <c r="R20" t="n">
-        <v>7288353</v>
+        <v>7288418</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2577,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128791263</v>
+        <v>128791243</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>80168</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769526</v>
+        <v>769412</v>
       </c>
       <c r="R21" t="n">
-        <v>7288515</v>
+        <v>7288353</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2648,11 +2653,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>128791250</v>
       </c>
       <c r="B8" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791260</v>
+        <v>128791252</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769511</v>
+        <v>769512</v>
       </c>
       <c r="R9" t="n">
-        <v>7288583</v>
+        <v>7288612</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791252</v>
+        <v>128791260</v>
       </c>
       <c r="B10" t="n">
-        <v>80139</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769512</v>
+        <v>769511</v>
       </c>
       <c r="R10" t="n">
-        <v>7288612</v>
+        <v>7288583</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1605,7 +1605,7 @@
         <v>128791261</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,32 +1801,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791254</v>
+        <v>128791257</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>769524</v>
+        <v>769534</v>
       </c>
       <c r="R13" t="n">
-        <v>7288630</v>
+        <v>7288588</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1898,32 +1898,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791257</v>
+        <v>128791254</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>80140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>769534</v>
+        <v>769524</v>
       </c>
       <c r="R14" t="n">
-        <v>7288588</v>
+        <v>7288630</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1998,7 +1998,7 @@
         <v>128791262</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128791266</v>
       </c>
       <c r="B16" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128791236</v>
       </c>
       <c r="B17" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>128791245</v>
       </c>
       <c r="B18" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128791263</v>
+        <v>128791237</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>91526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2394,21 +2394,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769526</v>
+        <v>769415</v>
       </c>
       <c r="R19" t="n">
-        <v>7288515</v>
+        <v>7288418</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2454,11 +2454,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2485,10 +2480,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128791237</v>
+        <v>128791263</v>
       </c>
       <c r="B20" t="n">
-        <v>91523</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2496,21 +2491,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769415</v>
+        <v>769526</v>
       </c>
       <c r="R20" t="n">
-        <v>7288418</v>
+        <v>7288515</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2556,6 +2551,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2585,7 +2585,7 @@
         <v>128791243</v>
       </c>
       <c r="B21" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>128791258</v>
       </c>
       <c r="B22" t="n">
-        <v>79113</v>
+        <v>79114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791242</v>
+        <v>128791264</v>
       </c>
       <c r="B23" t="n">
-        <v>80168</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769513</v>
+        <v>769507</v>
       </c>
       <c r="R23" t="n">
-        <v>7288611</v>
+        <v>7288631</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791244</v>
+        <v>128791242</v>
       </c>
       <c r="B24" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769510</v>
+        <v>769513</v>
       </c>
       <c r="R24" t="n">
-        <v>7288634</v>
+        <v>7288611</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791264</v>
+        <v>128791244</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>80169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769507</v>
+        <v>769510</v>
       </c>
       <c r="R25" t="n">
-        <v>7288631</v>
+        <v>7288634</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791252</v>
+        <v>128791260</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769512</v>
+        <v>769511</v>
       </c>
       <c r="R9" t="n">
-        <v>7288612</v>
+        <v>7288583</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791260</v>
+        <v>128791252</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769511</v>
+        <v>769512</v>
       </c>
       <c r="R10" t="n">
-        <v>7288583</v>
+        <v>7288612</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1801,32 +1801,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791257</v>
+        <v>128791254</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>769534</v>
+        <v>769524</v>
       </c>
       <c r="R13" t="n">
-        <v>7288588</v>
+        <v>7288630</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1898,32 +1898,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791254</v>
+        <v>128791257</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>769524</v>
+        <v>769534</v>
       </c>
       <c r="R14" t="n">
-        <v>7288630</v>
+        <v>7288588</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791260</v>
+        <v>128791252</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769511</v>
+        <v>769512</v>
       </c>
       <c r="R9" t="n">
-        <v>7288583</v>
+        <v>7288612</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791252</v>
+        <v>128791260</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769512</v>
+        <v>769511</v>
       </c>
       <c r="R10" t="n">
-        <v>7288612</v>
+        <v>7288583</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1801,32 +1801,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791254</v>
+        <v>128791257</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>769524</v>
+        <v>769534</v>
       </c>
       <c r="R13" t="n">
-        <v>7288630</v>
+        <v>7288588</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1898,32 +1898,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791257</v>
+        <v>128791254</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>769534</v>
+        <v>769524</v>
       </c>
       <c r="R14" t="n">
-        <v>7288588</v>
+        <v>7288630</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>128791250</v>
       </c>
       <c r="B8" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128791252</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128791260</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128791261</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128791238</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>128791257</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>128791254</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>128791262</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128791266</v>
       </c>
       <c r="B16" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128791236</v>
       </c>
       <c r="B17" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>128791245</v>
       </c>
       <c r="B18" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128791237</v>
+        <v>128791263</v>
       </c>
       <c r="B19" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2394,21 +2394,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769415</v>
+        <v>769526</v>
       </c>
       <c r="R19" t="n">
-        <v>7288418</v>
+        <v>7288515</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2454,6 +2454,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2480,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128791263</v>
+        <v>128791237</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>91533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2491,21 +2496,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769526</v>
+        <v>769415</v>
       </c>
       <c r="R20" t="n">
-        <v>7288515</v>
+        <v>7288418</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2551,11 +2556,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2585,7 +2585,7 @@
         <v>128791243</v>
       </c>
       <c r="B21" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>128791258</v>
       </c>
       <c r="B22" t="n">
-        <v>79114</v>
+        <v>79118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>128791264</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>128791242</v>
       </c>
       <c r="B24" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128791244</v>
       </c>
       <c r="B25" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1801,32 +1801,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791257</v>
+        <v>128791254</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>769534</v>
+        <v>769524</v>
       </c>
       <c r="R13" t="n">
-        <v>7288588</v>
+        <v>7288630</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1898,32 +1898,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791254</v>
+        <v>128791257</v>
       </c>
       <c r="B14" t="n">
-        <v>80144</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>769524</v>
+        <v>769534</v>
       </c>
       <c r="R14" t="n">
-        <v>7288630</v>
+        <v>7288588</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791264</v>
+        <v>128791242</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>80173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769507</v>
+        <v>769513</v>
       </c>
       <c r="R23" t="n">
-        <v>7288631</v>
+        <v>7288611</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2873,7 +2873,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791242</v>
+        <v>128791244</v>
       </c>
       <c r="B24" t="n">
         <v>80173</v>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769513</v>
+        <v>769510</v>
       </c>
       <c r="R24" t="n">
-        <v>7288611</v>
+        <v>7288634</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791244</v>
+        <v>128791264</v>
       </c>
       <c r="B25" t="n">
-        <v>80173</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769510</v>
+        <v>769507</v>
       </c>
       <c r="R25" t="n">
-        <v>7288634</v>
+        <v>7288631</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>128791250</v>
       </c>
       <c r="B8" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128791252</v>
+        <v>128791260</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769512</v>
+        <v>769511</v>
       </c>
       <c r="R9" t="n">
-        <v>7288612</v>
+        <v>7288583</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791260</v>
+        <v>128791252</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769511</v>
+        <v>769512</v>
       </c>
       <c r="R10" t="n">
-        <v>7288583</v>
+        <v>7288612</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1901,7 +1901,7 @@
         <v>128791257</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128791266</v>
       </c>
       <c r="B16" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128791236</v>
       </c>
       <c r="B17" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128791263</v>
+        <v>128791243</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>80173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769526</v>
+        <v>769412</v>
       </c>
       <c r="R19" t="n">
-        <v>7288515</v>
+        <v>7288353</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2454,11 +2454,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2488,7 +2483,7 @@
         <v>128791237</v>
       </c>
       <c r="B20" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,32 +2577,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128791243</v>
+        <v>128791263</v>
       </c>
       <c r="B21" t="n">
-        <v>80173</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769412</v>
+        <v>769526</v>
       </c>
       <c r="R21" t="n">
-        <v>7288353</v>
+        <v>7288515</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2653,6 +2648,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791242</v>
+        <v>128791264</v>
       </c>
       <c r="B23" t="n">
-        <v>80173</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769513</v>
+        <v>769507</v>
       </c>
       <c r="R23" t="n">
-        <v>7288611</v>
+        <v>7288631</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2873,7 +2873,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791244</v>
+        <v>128791242</v>
       </c>
       <c r="B24" t="n">
         <v>80173</v>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769510</v>
+        <v>769513</v>
       </c>
       <c r="R24" t="n">
-        <v>7288634</v>
+        <v>7288611</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791264</v>
+        <v>128791244</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>80173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769507</v>
+        <v>769510</v>
       </c>
       <c r="R25" t="n">
-        <v>7288631</v>
+        <v>7288634</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>128791250</v>
       </c>
       <c r="B8" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128791260</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128791252</v>
       </c>
       <c r="B10" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128791261</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128791238</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>128791254</v>
       </c>
       <c r="B13" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>128791257</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>128791262</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128791266</v>
       </c>
       <c r="B16" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128791236</v>
       </c>
       <c r="B17" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>128791245</v>
       </c>
       <c r="B18" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128791243</v>
+        <v>128791237</v>
       </c>
       <c r="B19" t="n">
-        <v>80173</v>
+        <v>91542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769412</v>
+        <v>769415</v>
       </c>
       <c r="R19" t="n">
-        <v>7288353</v>
+        <v>7288418</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128791237</v>
+        <v>128791263</v>
       </c>
       <c r="B20" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2491,21 +2491,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769415</v>
+        <v>769526</v>
       </c>
       <c r="R20" t="n">
-        <v>7288418</v>
+        <v>7288515</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2551,6 +2551,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2577,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128791263</v>
+        <v>128791243</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>80175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769526</v>
+        <v>769412</v>
       </c>
       <c r="R21" t="n">
-        <v>7288515</v>
+        <v>7288353</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2648,11 +2653,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2682,7 +2682,7 @@
         <v>128791258</v>
       </c>
       <c r="B22" t="n">
-        <v>79118</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>128791264</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>128791242</v>
       </c>
       <c r="B24" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128791244</v>
       </c>
       <c r="B25" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -2383,10 +2383,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128791237</v>
+        <v>128791263</v>
       </c>
       <c r="B19" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2394,21 +2394,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769415</v>
+        <v>769526</v>
       </c>
       <c r="R19" t="n">
-        <v>7288418</v>
+        <v>7288515</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2454,6 +2454,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2480,32 +2485,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128791263</v>
+        <v>128791243</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769526</v>
+        <v>769412</v>
       </c>
       <c r="R20" t="n">
-        <v>7288515</v>
+        <v>7288353</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2551,11 +2556,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2582,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128791243</v>
+        <v>128791237</v>
       </c>
       <c r="B21" t="n">
-        <v>80175</v>
+        <v>91542</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769412</v>
+        <v>769415</v>
       </c>
       <c r="R21" t="n">
-        <v>7288353</v>
+        <v>7288418</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1801,32 +1801,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128791254</v>
+        <v>128791257</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>769524</v>
+        <v>769534</v>
       </c>
       <c r="R13" t="n">
-        <v>7288630</v>
+        <v>7288588</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1898,32 +1898,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128791257</v>
+        <v>128791254</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>769534</v>
+        <v>769524</v>
       </c>
       <c r="R14" t="n">
-        <v>7288588</v>
+        <v>7288630</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128791263</v>
+        <v>128791243</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769526</v>
+        <v>769412</v>
       </c>
       <c r="R19" t="n">
-        <v>7288515</v>
+        <v>7288353</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2454,11 +2454,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2485,32 +2480,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128791243</v>
+        <v>128791237</v>
       </c>
       <c r="B20" t="n">
-        <v>80175</v>
+        <v>91542</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769412</v>
+        <v>769415</v>
       </c>
       <c r="R20" t="n">
-        <v>7288353</v>
+        <v>7288418</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2582,10 +2577,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128791237</v>
+        <v>128791263</v>
       </c>
       <c r="B21" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,21 +2588,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769415</v>
+        <v>769526</v>
       </c>
       <c r="R21" t="n">
-        <v>7288418</v>
+        <v>7288515</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2653,6 +2648,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>50cm lång</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128791264</v>
+        <v>128791242</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769507</v>
+        <v>769513</v>
       </c>
       <c r="R23" t="n">
-        <v>7288631</v>
+        <v>7288611</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2873,7 +2873,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128791242</v>
+        <v>128791244</v>
       </c>
       <c r="B24" t="n">
         <v>80175</v>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>769513</v>
+        <v>769510</v>
       </c>
       <c r="R24" t="n">
-        <v>7288611</v>
+        <v>7288634</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128791244</v>
+        <v>128791264</v>
       </c>
       <c r="B25" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769510</v>
+        <v>769507</v>
       </c>
       <c r="R25" t="n">
-        <v>7288634</v>
+        <v>7288631</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 45427-2025 artfynd.xlsx
+++ b/artfynd/A 45427-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>128791250</v>
       </c>
       <c r="B8" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>128791257</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128791236</v>
       </c>
       <c r="B17" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>128791237</v>
       </c>
       <c r="B20" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
